--- a/Assets/Game_Design/무기 디자인.xlsx
+++ b/Assets/Game_Design/무기 디자인.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>1열</t>
   </si>
@@ -33,6 +33,15 @@
     <t>5열</t>
   </si>
   <si>
+    <t>9열</t>
+  </si>
+  <si>
+    <t>10열</t>
+  </si>
+  <si>
+    <t>11열</t>
+  </si>
+  <si>
     <t>6열</t>
   </si>
   <si>
@@ -57,7 +66,16 @@
     <t>공격 속도</t>
   </si>
   <si>
-    <t>이동 속도</t>
+    <t>걷는 이동 속도</t>
+  </si>
+  <si>
+    <t>뛰는 이동 속도</t>
+  </si>
+  <si>
+    <t>앉아서 이동 속도</t>
+  </si>
+  <si>
+    <t>포복 이동 속도</t>
   </si>
   <si>
     <t>난이도</t>
@@ -78,7 +96,19 @@
     <t>100(고정)</t>
   </si>
   <si>
-    <t>5(빠름)</t>
+    <t>1(빠름)</t>
+  </si>
+  <si>
+    <t>1.5(빠름)</t>
+  </si>
+  <si>
+    <t>3(빠름)</t>
+  </si>
+  <si>
+    <t>0.825(빠름)</t>
+  </si>
+  <si>
+    <t>0.525(빠름)</t>
   </si>
   <si>
     <t>2(쉬움)</t>
@@ -96,6 +126,21 @@
     <t>4(보통)</t>
   </si>
   <si>
+    <t>0.85(보통)</t>
+  </si>
+  <si>
+    <t>1.05(보통)</t>
+  </si>
+  <si>
+    <t>2.1(보통)</t>
+  </si>
+  <si>
+    <t>0.5775(보통)</t>
+  </si>
+  <si>
+    <t>0.3675(보통)</t>
+  </si>
+  <si>
     <t>3(보통)</t>
   </si>
   <si>
@@ -108,7 +153,19 @@
     <t>6(김)</t>
   </si>
   <si>
-    <t>2(느림)</t>
+    <t>0.7(느림)</t>
+  </si>
+  <si>
+    <t>0.9(느림)</t>
+  </si>
+  <si>
+    <t>1.8(느림)</t>
+  </si>
+  <si>
+    <t>0.495(느림)</t>
+  </si>
+  <si>
+    <t>0.315(느림)</t>
   </si>
   <si>
     <t>4(어려움)</t>
@@ -121,7 +178,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -142,6 +199,11 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -151,50 +213,8 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF356854"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF356854"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF356854"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF356854"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-    </border>
     <border>
       <left style="thin">
         <color rgb="FF284E3F"/>
@@ -325,72 +345,75 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font/>
       <fill>
@@ -428,13 +451,29 @@
       </fill>
       <border/>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle count="4" pivot="0" name="무기 정리-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement size="0" type="wholeTable"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -445,16 +484,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H5" displayName="표1" name="표1" id="1">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K5" displayName="표1" name="표1" id="1">
+  <tableColumns count="11">
     <tableColumn name="1열" id="1"/>
     <tableColumn name="2열" id="2"/>
     <tableColumn name="3열" id="3"/>
     <tableColumn name="4열" id="4"/>
     <tableColumn name="5열" id="5"/>
-    <tableColumn name="6열" id="6"/>
-    <tableColumn name="7열" id="7"/>
-    <tableColumn name="8열" id="8"/>
+    <tableColumn name="9열" id="6"/>
+    <tableColumn name="10열" id="7"/>
+    <tableColumn name="11열" id="8"/>
+    <tableColumn name="6열" id="9"/>
+    <tableColumn name="7열" id="10"/>
+    <tableColumn name="8열" id="11"/>
   </tableColumns>
   <tableStyleInfo name="무기 정리-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -661,138 +703,191 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="7" width="22.63"/>
-    <col customWidth="1" min="8" max="8" width="36.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="10.88"/>
+    <col customWidth="1" min="3" max="4" width="12.13"/>
+    <col customWidth="1" min="5" max="5" width="15.5"/>
+    <col customWidth="1" min="6" max="6" width="15.25"/>
+    <col customWidth="1" min="7" max="7" width="16.63"/>
+    <col customWidth="1" min="8" max="8" width="17.88"/>
+    <col customWidth="1" min="9" max="9" width="20.0"/>
+    <col customWidth="1" min="10" max="10" width="19.75"/>
+    <col customWidth="1" min="11" max="11" width="44.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>27</v>
+      <c r="E4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>32</v>
+      <c r="A5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1"/>
